--- a/backend/static/reporte_demanda.xlsx
+++ b/backend/static/reporte_demanda.xlsx
@@ -464,19 +464,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.572</v>
+        <v>1.04</v>
       </c>
       <c r="C4" t="n">
-        <v>1.266</v>
+        <v>0.964</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.289</v>
+        <v>0.46</v>
       </c>
       <c r="E4" t="n">
-        <v>87.97</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>4.36</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="5">
@@ -486,19 +486,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.488</v>
+        <v>1.677</v>
       </c>
       <c r="C5" t="n">
-        <v>1.009</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.154</v>
+        <v>-0.406</v>
       </c>
       <c r="E5" t="n">
-        <v>54.05</v>
+        <v>60.88</v>
       </c>
       <c r="F5" t="n">
-        <v>245.25</v>
+        <v>101.54</v>
       </c>
     </row>
     <row r="6">
@@ -508,19 +508,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.096</v>
+        <v>1.508</v>
       </c>
       <c r="C6" t="n">
-        <v>1.741</v>
+        <v>1.331</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.29</v>
+        <v>-0.137</v>
       </c>
       <c r="E6" t="n">
-        <v>118.64</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>528.64</v>
+        <v>161.66</v>
       </c>
     </row>
     <row r="7">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.188</v>
+        <v>1.808</v>
       </c>
       <c r="C7" t="n">
-        <v>1.828</v>
+        <v>1.36</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.495</v>
+        <v>-0.635</v>
       </c>
       <c r="E7" t="n">
-        <v>130.7</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>600.23</v>
+        <v>188.94</v>
       </c>
     </row>
     <row r="8">
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.609</v>
+        <v>1.422</v>
       </c>
       <c r="C8" t="n">
-        <v>1.537</v>
+        <v>1.224</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.349</v>
+        <v>-0.011</v>
       </c>
       <c r="E8" t="n">
-        <v>121.84</v>
+        <v>61.79</v>
       </c>
       <c r="F8" t="n">
-        <v>1504.57</v>
+        <v>823.9</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +575,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
     </row>
@@ -628,15 +628,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -674,15 +674,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -728,7 +728,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -743,15 +743,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -789,15 +789,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -881,15 +881,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sábado, 18 de julio de 2026</t>
+          <t>martes, 21 de julio de 2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -904,15 +904,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -950,15 +950,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -981,7 +981,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1019,15 +1019,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1065,15 +1065,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1111,15 +1111,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1157,15 +1157,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>domingo, 19 de julio de 2026</t>
+          <t>miércoles, 22 de julio de 2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1180,15 +1180,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1226,15 +1226,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1249,15 +1249,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1272,15 +1272,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1295,15 +1295,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1387,15 +1387,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1410,15 +1410,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1433,15 +1433,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lunes, 20 de julio de 2026</t>
+          <t>jueves, 23 de julio de 2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1456,15 +1456,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1479,15 +1479,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1502,15 +1502,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1525,15 +1525,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1548,15 +1548,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1571,15 +1571,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1594,15 +1594,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1617,15 +1617,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1686,15 +1686,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>martes, 21 de julio de 2026</t>
+          <t>viernes, 24 de julio de 2026</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1732,15 +1732,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1801,15 +1801,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1939,15 +1939,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1962,15 +1962,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1985,15 +1985,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>miércoles, 22 de julio de 2026</t>
+          <t>sábado, 25 de julio de 2026</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2008,15 +2008,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2054,15 +2054,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2123,15 +2123,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2169,15 +2169,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2261,15 +2261,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jueves, 23 de julio de 2026</t>
+          <t>domingo, 26 de julio de 2026</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2376,15 +2376,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2445,15 +2445,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2537,15 +2537,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>viernes, 24 de julio de 2026</t>
+          <t>lunes, 27 de julio de 2026</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Regresion Lineal</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="4">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="5">
@@ -2682,7 +2682,7 @@
         <v>3.5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.082207001484488</v>
+        <v>2.618614682831908</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -2758,7 +2758,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>1.154700538379251</v>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="C19" t="n">
-        <v>1.732050807568877</v>
+        <v>1.5</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2891,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
